--- a/gu_in/Map.edf/Platform01.xlsx
+++ b/gu_in/Map.edf/Platform01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\emay.dev\Parser_1.0.2\Database\gu_in\Map.edf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D72757-5D76-4FDC-82E6-A292F0727B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01C55B0-A43F-4810-AC92-3E4F280A4B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5265" yWindow="1080" windowWidth="17565" windowHeight="11205" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6330" yWindow="1050" windowWidth="17565" windowHeight="11205" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4989" uniqueCount="2122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4991" uniqueCount="2124">
   <si>
     <t>char[32]</t>
   </si>
@@ -6404,6 +6404,12 @@
   </si>
   <si>
     <t>bdC31E5</t>
+  </si>
+  <si>
+    <t>sdC31E6</t>
+  </si>
+  <si>
+    <t>bdC31E6</t>
   </si>
 </sst>
 </file>
@@ -6456,7 +6462,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -78522,7 +78548,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -82841,23 +82867,81 @@
         <v>120</v>
       </c>
     </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="2" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B167" s="1">
+        <v>0</v>
+      </c>
+      <c r="C167" s="1">
+        <v>-6883</v>
+      </c>
+      <c r="D167" s="1">
+        <v>608</v>
+      </c>
+      <c r="E167" s="1">
+        <v>927</v>
+      </c>
+      <c r="F167" s="1">
+        <v>20</v>
+      </c>
+      <c r="G167" s="1">
+        <v>20</v>
+      </c>
+      <c r="H167" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="2" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B168" s="1">
+        <v>0</v>
+      </c>
+      <c r="C168" s="1">
+        <v>-6883</v>
+      </c>
+      <c r="D168" s="1">
+        <v>608</v>
+      </c>
+      <c r="E168" s="1">
+        <v>927</v>
+      </c>
+      <c r="F168" s="1">
+        <v>80</v>
+      </c>
+      <c r="G168" s="1">
+        <v>40</v>
+      </c>
+      <c r="H168" s="1">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A161">
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A162">
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A163">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A162">
+  <conditionalFormatting sqref="A164">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A163">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  <conditionalFormatting sqref="A165">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A164">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="A166">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A165">
+  <conditionalFormatting sqref="A167">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A166">
+  <conditionalFormatting sqref="A168">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
